--- a/business-libraries/test-data/home_school/assessment.xlsx
+++ b/business-libraries/test-data/home_school/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:Q3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,102 +419,51 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
-        <v>适用年级</v>
+        <v>施测对象*</v>
       </c>
       <c r="G1" t="str">
-        <v>适用学科</v>
+        <v>施测形式*</v>
       </c>
       <c r="H1" t="str">
-        <v>施测对象*</v>
+        <v>触发方式*</v>
       </c>
       <c r="I1" t="str">
-        <v>施测形式*</v>
+        <v>作答频次*</v>
       </c>
       <c r="J1" t="str">
-        <v>触发方式*</v>
+        <v>是否必做*</v>
       </c>
       <c r="K1" t="str">
-        <v>作答频次*</v>
+        <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
-        <v>是否必做*</v>
+        <v>结果可见性*</v>
       </c>
       <c r="M1" t="str">
-        <v>预计用时分钟*</v>
+        <v>数据敏感级*</v>
       </c>
       <c r="N1" t="str">
-        <v>作答时限分钟</v>
+        <v>来源属性*</v>
       </c>
       <c r="O1" t="str">
-        <v>最低题数</v>
+        <v>手册出处*</v>
       </c>
       <c r="P1" t="str">
-        <v>使用时机</v>
+        <v>版本*</v>
       </c>
       <c r="Q1" t="str">
-        <v>重评间隔天数</v>
-      </c>
-      <c r="R1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="S1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="T1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>责任角色</v>
-      </c>
-      <c r="V1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="W1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="X1" t="str">
-        <v>外部授权说明</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="AA1" t="str">
         <v>量表说明</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>常模参照</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>信度说明</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>效度说明</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>隐私声明</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>适用前提</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>不适合情况</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>后续建议动作</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B2" t="str">
-        <v>家校沟通合作家校沟通五问</v>
+        <v>家校沟通双维与容器速查</v>
       </c>
       <c r="C2" t="str">
-        <v>家校沟通</v>
+        <v>双维速查</v>
       </c>
       <c r="D2" t="str">
         <v>home_school</v>
@@ -523,102 +472,51 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H2" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I2" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J2" t="str">
-        <v>manual</v>
+        <v>是</v>
       </c>
       <c r="K2" t="str">
-        <v>monthly</v>
+        <v>5</v>
       </c>
       <c r="L2" t="str">
-        <v>是</v>
+        <v>teacher_only</v>
       </c>
       <c r="M2" t="str">
-        <v>3</v>
+        <v>sensitive</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="O2" t="str">
-        <v>5</v>
+        <v>家校沟通合作手册v1</v>
       </c>
       <c r="P2" t="str">
-        <v>每月一次</v>
+        <v>1.0.0</v>
       </c>
       <c r="Q2" t="str">
-        <v>30</v>
-      </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="U2" t="str">
-        <v>班主任本人</v>
-      </c>
-      <c r="V2" t="str">
-        <v>highly_sensitive</v>
-      </c>
-      <c r="W2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v>技术理论手册V5 第3章</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>回顾最近一周状态，产出多维评估结果</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>全国中小学班主任常模 N=3200</v>
-      </c>
-      <c r="AC2" t="str">
-        <v>Cronbach α=0.87</v>
-      </c>
-      <c r="AD2" t="str">
-        <v>与GHQ-12 相关系数 r=0.64</v>
-      </c>
-      <c r="AE2" t="str">
-        <v>数据仅用于教学支持，不用于人事考核</v>
-      </c>
-      <c r="AF2" t="str">
-        <v>适用于在职班主任，不适用于实习或代课教师</v>
-      </c>
-      <c r="AG2" t="str">
-        <v>教师正在经历重大个人变故时，建议先转介心理支持再施测</v>
-      </c>
-      <c r="AH2" t="str">
-        <v>如总分&gt;=17，建议进行深度访谈并启动个案</v>
+        <v>判断家长配合度、沟通态度和当前关系容器。反向计分：得分越高表示状况越差。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B3" t="str">
-        <v>家校沟通合作家长参与度评估</v>
+        <v>家长分型与沟通策略评估</v>
       </c>
       <c r="C3" t="str">
-        <v>家长参与</v>
+        <v>家长分型</v>
       </c>
       <c r="D3" t="str">
         <v>home_school</v>
@@ -627,103 +525,52 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H3" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I3" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J3" t="str">
-        <v>manual</v>
+        <v>否</v>
       </c>
       <c r="K3" t="str">
-        <v>per_case</v>
+        <v>6</v>
       </c>
       <c r="L3" t="str">
-        <v>是</v>
+        <v>teacher_only</v>
       </c>
       <c r="M3" t="str">
-        <v>5</v>
+        <v>sensitive</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="O3" t="str">
-        <v>8</v>
+        <v>家校沟通合作手册v1</v>
       </c>
       <c r="P3" t="str">
-        <v>学期初/学期末</v>
+        <v>1.0.0</v>
       </c>
       <c r="Q3" t="str">
-        <v>90</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="U3" t="str">
-        <v>班主任本人</v>
-      </c>
-      <c r="V3" t="str">
-        <v>internal</v>
-      </c>
-      <c r="W3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <v>技术理论手册V5 第4章</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>评估教师在家校沟通合作相关维度的资源与压力状况</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>全国中小学班主任常模 N=2800</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>Cronbach α=0.82</v>
-      </c>
-      <c r="AD3" t="str">
-        <v>内容效度经专家评审</v>
-      </c>
-      <c r="AE3" t="str">
-        <v>数据仅用于教学支持</v>
-      </c>
-      <c r="AF3" t="str">
-        <v>适用于在职班主任</v>
-      </c>
-      <c r="AG3" t="str">
-        <v>教师在严重心理危机时，建议先进行心理评估</v>
-      </c>
-      <c r="AH3" t="str">
-        <v>根据评估结果推荐相应的支持工具</v>
+        <v>在双维速查提示需要重点沟通后使用，用于判断家长互动模式并匹配沟通策略。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:J16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -739,290 +586,182 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
-        <v>子维度</v>
+        <v>题干*</v>
       </c>
       <c r="F1" t="str">
-        <v>题干*</v>
+        <v>选项组编码*</v>
       </c>
       <c r="G1" t="str">
-        <v>题干举例</v>
+        <v>反向计分*</v>
       </c>
       <c r="H1" t="str">
-        <v>选项组编码*</v>
+        <v>权重</v>
       </c>
       <c r="I1" t="str">
-        <v>反向计分*</v>
+        <v>是否必答*</v>
       </c>
       <c r="J1" t="str">
-        <v>权重</v>
-      </c>
-      <c r="K1" t="str">
-        <v>是否必答*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>显示条件</v>
-      </c>
-      <c r="M1" t="str">
         <v>数据用途*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>答题提示</v>
-      </c>
-      <c r="O1" t="str">
-        <v>题目说明</v>
-      </c>
-      <c r="P1" t="str">
-        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B2" t="str">
-        <v>q1</v>
+        <v>coop1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>COMM_QUALITY</v>
+        <v>配合度</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>家长能够及时回应学校的重要沟通。</v>
       </c>
       <c r="F2" t="str">
-        <v>这一周，我有多少时间感到与家长沟通的质量和频率？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H2" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>1</v>
-      </c>
-      <c r="K2" t="str">
-        <v>是</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
         <v>compute</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B3" t="str">
-        <v>q2</v>
+        <v>coop2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
       </c>
       <c r="D3" t="str">
-        <v>TRUST</v>
+        <v>配合度</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>家长愿意共同讨论并执行已经达成的行动。</v>
       </c>
       <c r="F3" t="str">
-        <v>这一周，我有多少时间感到家长对教师的信任程度？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H3" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J3" t="str">
-        <v>1</v>
-      </c>
-      <c r="K3" t="str">
-        <v>是</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
         <v>compute</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B4" t="str">
-        <v>q3</v>
+        <v>coop3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
       </c>
       <c r="D4" t="str">
-        <v>ENGAGEMENT</v>
+        <v>配合度</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>出现分歧后，家长仍愿意继续保持沟通。</v>
       </c>
       <c r="F4" t="str">
-        <v>这一周，我有多少时间感到家长参与教育活动的积极性？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H4" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
-        <v>1</v>
-      </c>
-      <c r="K4" t="str">
-        <v>是</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
         <v>compute</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B5" t="str">
-        <v>q4</v>
+        <v>att1</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>CONFLICT</v>
+        <v>沟通态度</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>家长表达不满时仍能保持基本尊重。</v>
       </c>
       <c r="F5" t="str">
-        <v>这一周，我有多少时间感到家校冲突的频率和强度？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H5" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J5" t="str">
-        <v>1</v>
-      </c>
-      <c r="K5" t="str">
-        <v>是</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
         <v>compute</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B6" t="str">
-        <v>q5</v>
+        <v>att2</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>SUPPORT</v>
+        <v>沟通态度</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>家长能够区分事实、推测和情绪。</v>
       </c>
       <c r="F6" t="str">
-        <v>这一周，我有多少时间感到家庭对学生学习的支持程度？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H6" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J6" t="str">
-        <v>1</v>
-      </c>
-      <c r="K6" t="str">
-        <v>是</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
         <v>compute</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1030,49 +769,31 @@
         <v>HS_QUICK</v>
       </c>
       <c r="B7" t="str">
-        <v>q1</v>
+        <v>att3</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>COMM_QUALITY</v>
+        <v>沟通态度</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>家长没有出现威胁、公开抹黑或恶意维权行为。</v>
       </c>
       <c r="F7" t="str">
-        <v>在家校沟通合作方面，评估与家长沟通的质量和频率的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H7" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J7" t="str">
-        <v>1</v>
-      </c>
-      <c r="K7" t="str">
-        <v>是</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
         <v>compute</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1080,49 +801,31 @@
         <v>HS_QUICK</v>
       </c>
       <c r="B8" t="str">
-        <v>q2</v>
+        <v>con1</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>TRUST</v>
+        <v>关系容器</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>目前的关系可以承受一次坦诚而具体的讨论。</v>
       </c>
       <c r="F8" t="str">
-        <v>在家校沟通合作方面，评估家长对教师的信任程度的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H8" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J8" t="str">
-        <v>1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>是</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
         <v>compute</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1130,49 +833,31 @@
         <v>HS_QUICK</v>
       </c>
       <c r="B9" t="str">
-        <v>q3</v>
+        <v>con2</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>ENGAGEMENT</v>
+        <v>关系容器</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>双方能够在情绪出现时暂停并回到问题解决。</v>
       </c>
       <c r="F9" t="str">
-        <v>在家校沟通合作方面，评估家长参与教育活动的积极性的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H9" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
-        <v>1</v>
-      </c>
-      <c r="K9" t="str">
-        <v>是</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
         <v>compute</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1180,111 +865,235 @@
         <v>HS_QUICK</v>
       </c>
       <c r="B10" t="str">
-        <v>q4</v>
+        <v>con3</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>CONFLICT</v>
+        <v>关系容器</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>过去的积极沟通经验仍能成为当前关系资源。</v>
       </c>
       <c r="F10" t="str">
-        <v>在家校沟通合作方面，评估家校冲突的频率和强度的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H10" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J10" t="str">
-        <v>1</v>
-      </c>
-      <c r="K10" t="str">
-        <v>是</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
         <v>compute</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B11" t="str">
-        <v>q5</v>
+        <v>p1</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>SUPPORT</v>
+        <v>焦虑水平</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>家长在沟通中反复确认同一件事。</v>
       </c>
       <c r="F11" t="str">
-        <v>在家校沟通合作方面，评估家庭对学生学习的支持程度的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H11" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J11" t="str">
-        <v>1</v>
-      </c>
-      <c r="K11" t="str">
-        <v>是</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
         <v>compute</v>
       </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v>5</v>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="B12" t="str">
+        <v>p2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>single</v>
+      </c>
+      <c r="D12" t="str">
+        <v>焦虑水平</v>
+      </c>
+      <c r="E12" t="str">
+        <v>家长常在非工作时间发来紧急消息。</v>
+      </c>
+      <c r="F12" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G12" t="str">
+        <v>是</v>
+      </c>
+      <c r="H12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I12" t="str">
+        <v>是</v>
+      </c>
+      <c r="J12" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="B13" t="str">
+        <v>p3</v>
+      </c>
+      <c r="C13" t="str">
+        <v>single</v>
+      </c>
+      <c r="D13" t="str">
+        <v>控制倾向</v>
+      </c>
+      <c r="E13" t="str">
+        <v>家长会具体指定学校应该如何处理。</v>
+      </c>
+      <c r="F13" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G13" t="str">
+        <v>是</v>
+      </c>
+      <c r="H13" t="str">
+        <v>1</v>
+      </c>
+      <c r="I13" t="str">
+        <v>是</v>
+      </c>
+      <c r="J13" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="B14" t="str">
+        <v>p4</v>
+      </c>
+      <c r="C14" t="str">
+        <v>single</v>
+      </c>
+      <c r="D14" t="str">
+        <v>控制倾向</v>
+      </c>
+      <c r="E14" t="str">
+        <v>家长对学校既有安排提出较多质疑。</v>
+      </c>
+      <c r="F14" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G14" t="str">
+        <v>是</v>
+      </c>
+      <c r="H14" t="str">
+        <v>1</v>
+      </c>
+      <c r="I14" t="str">
+        <v>是</v>
+      </c>
+      <c r="J14" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="B15" t="str">
+        <v>p5</v>
+      </c>
+      <c r="C15" t="str">
+        <v>single</v>
+      </c>
+      <c r="D15" t="str">
+        <v>信任基础</v>
+      </c>
+      <c r="E15" t="str">
+        <v>家长相信教师是出于孩子利益在做判断。</v>
+      </c>
+      <c r="F15" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G15" t="str">
+        <v>是</v>
+      </c>
+      <c r="H15" t="str">
+        <v>1</v>
+      </c>
+      <c r="I15" t="str">
+        <v>是</v>
+      </c>
+      <c r="J15" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>HS_PARENT_TYPE</v>
+      </c>
+      <c r="B16" t="str">
+        <v>p6</v>
+      </c>
+      <c r="C16" t="str">
+        <v>single</v>
+      </c>
+      <c r="D16" t="str">
+        <v>信任基础</v>
+      </c>
+      <c r="E16" t="str">
+        <v>过去的沟通中，家长兑现过共同约定。</v>
+      </c>
+      <c r="F16" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G16" t="str">
+        <v>是</v>
+      </c>
+      <c r="H16" t="str">
+        <v>1</v>
+      </c>
+      <c r="I16" t="str">
+        <v>是</v>
+      </c>
+      <c r="J16" t="str">
+        <v>compute</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1370,16 +1179,86 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>3</v>
+      </c>
+      <c r="C9" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D9" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>4</v>
+      </c>
+      <c r="C10" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B11" t="str">
+        <v>5</v>
+      </c>
+      <c r="C11" t="str">
+        <v>非常符合</v>
+      </c>
+      <c r="D11" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:I7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1409,25 +1288,19 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
-      <c r="J1" t="str">
-        <v>常模均值</v>
-      </c>
-      <c r="K1" t="str">
-        <v>常模标准差</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B2" t="str">
-        <v>COMM_QUALITY</v>
+        <v>HS_COOP</v>
       </c>
       <c r="C2" t="str">
-        <v>沟通质量</v>
+        <v>配合度</v>
       </c>
       <c r="D2" t="str">
-        <v>q1</v>
+        <v>coop1,coop2,coop3</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1436,33 +1309,27 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>评估与家长沟通的质量和频率</v>
+        <v>配合度维度</v>
       </c>
       <c r="H2" t="str">
-        <v>&gt;=4 分：沟通顺畅</v>
+        <v>家长回应慢、不参与共同行动</v>
       </c>
       <c r="I2" t="str">
-        <v>&lt;=2 分：沟通障碍</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2.7</v>
-      </c>
-      <c r="K2" t="str">
-        <v>0.9</v>
+        <v>配合度良好</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B3" t="str">
-        <v>TRUST</v>
+        <v>HS_ATTITUDE</v>
       </c>
       <c r="C3" t="str">
-        <v>家长信任</v>
+        <v>沟通态度</v>
       </c>
       <c r="D3" t="str">
-        <v>q2</v>
+        <v>att1,att2,att3</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1471,33 +1338,27 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>评估家长对教师的信任程度</v>
+        <v>沟通态度维度</v>
       </c>
       <c r="H3" t="str">
-        <v>&gt;=4 分：信任度高</v>
+        <v>出现不尊重、混淆事实与情绪甚至威胁行为</v>
       </c>
       <c r="I3" t="str">
-        <v>&lt;=2 分：信任不足</v>
-      </c>
-      <c r="J3" t="str">
-        <v>3.0</v>
-      </c>
-      <c r="K3" t="str">
-        <v>0.85</v>
+        <v>沟通态度可控</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B4" t="str">
-        <v>ENGAGEMENT</v>
+        <v>HS_CONTAINER</v>
       </c>
       <c r="C4" t="str">
-        <v>家长参与</v>
+        <v>关系容器</v>
       </c>
       <c r="D4" t="str">
-        <v>q3</v>
+        <v>con1,con2,con3</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1506,33 +1367,27 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>评估家长参与教育活动的积极性</v>
+        <v>关系容器维度</v>
       </c>
       <c r="H4" t="str">
-        <v>&gt;=4 分：参与积极</v>
+        <v>关系无法承受坦诚讨论</v>
       </c>
       <c r="I4" t="str">
-        <v>&lt;=2 分：参与度低</v>
-      </c>
-      <c r="J4" t="str">
-        <v>2.5</v>
-      </c>
-      <c r="K4" t="str">
-        <v>0.95</v>
+        <v>关系容器充足</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B5" t="str">
-        <v>CONFLICT</v>
+        <v>HS_ANXIETY</v>
       </c>
       <c r="C5" t="str">
-        <v>家校冲突</v>
+        <v>焦虑水平</v>
       </c>
       <c r="D5" t="str">
-        <v>q4</v>
+        <v>p1,p2</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1541,33 +1396,27 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>评估家校冲突的频率和强度</v>
+        <v>焦虑水平维度</v>
       </c>
       <c r="H5" t="str">
-        <v>&gt;=4 分：冲突频发</v>
+        <v>家长处于高焦虑，难以接收复杂信息</v>
       </c>
       <c r="I5" t="str">
-        <v>&lt;=2 分：关系和谐</v>
-      </c>
-      <c r="J5" t="str">
-        <v>2.2</v>
-      </c>
-      <c r="K5" t="str">
-        <v>1.0</v>
+        <v>情绪相对平稳</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_FIVE_Q</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B6" t="str">
-        <v>SUPPORT</v>
+        <v>HS_CONTROL</v>
       </c>
       <c r="C6" t="str">
-        <v>家庭支持</v>
+        <v>控制倾向</v>
       </c>
       <c r="D6" t="str">
-        <v>q5</v>
+        <v>p3,p4</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1576,33 +1425,27 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>评估家庭对学生学习的支持程度</v>
+        <v>控制倾向维度</v>
       </c>
       <c r="H6" t="str">
-        <v>&gt;=4 分：支持充分</v>
+        <v>家长倾向于主导教育方式并质疑学校安排</v>
       </c>
       <c r="I6" t="str">
-        <v>&lt;=2 分：支持不足</v>
-      </c>
-      <c r="J6" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="K6" t="str">
-        <v>0.9</v>
+        <v>愿意接受学校专业判断</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B7" t="str">
-        <v>COMM_QUALITY</v>
+        <v>HS_TRUST</v>
       </c>
       <c r="C7" t="str">
-        <v>沟通质量</v>
+        <v>信任基础</v>
       </c>
       <c r="D7" t="str">
-        <v>q1</v>
+        <v>p5,p6</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1611,164 +1454,18 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>评估与家长沟通的质量和频率</v>
+        <v>信任基础维度</v>
       </c>
       <c r="H7" t="str">
-        <v>&gt;=4 分：沟通顺畅</v>
+        <v>对学校缺乏基本信任</v>
       </c>
       <c r="I7" t="str">
-        <v>&lt;=2 分：沟通障碍</v>
-      </c>
-      <c r="J7" t="str">
-        <v>2.7</v>
-      </c>
-      <c r="K7" t="str">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>HS_QUICK</v>
-      </c>
-      <c r="B8" t="str">
-        <v>TRUST</v>
-      </c>
-      <c r="C8" t="str">
-        <v>家长信任</v>
-      </c>
-      <c r="D8" t="str">
-        <v>q2</v>
-      </c>
-      <c r="E8" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F8" t="str">
-        <v>1</v>
-      </c>
-      <c r="G8" t="str">
-        <v>评估家长对教师的信任程度</v>
-      </c>
-      <c r="H8" t="str">
-        <v>&gt;=4 分：信任度高</v>
-      </c>
-      <c r="I8" t="str">
-        <v>&lt;=2 分：信任不足</v>
-      </c>
-      <c r="J8" t="str">
-        <v>3.0</v>
-      </c>
-      <c r="K8" t="str">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>HS_QUICK</v>
-      </c>
-      <c r="B9" t="str">
-        <v>ENGAGEMENT</v>
-      </c>
-      <c r="C9" t="str">
-        <v>家长参与</v>
-      </c>
-      <c r="D9" t="str">
-        <v>q3</v>
-      </c>
-      <c r="E9" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F9" t="str">
-        <v>1</v>
-      </c>
-      <c r="G9" t="str">
-        <v>评估家长参与教育活动的积极性</v>
-      </c>
-      <c r="H9" t="str">
-        <v>&gt;=4 分：参与积极</v>
-      </c>
-      <c r="I9" t="str">
-        <v>&lt;=2 分：参与度低</v>
-      </c>
-      <c r="J9" t="str">
-        <v>2.5</v>
-      </c>
-      <c r="K9" t="str">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>HS_QUICK</v>
-      </c>
-      <c r="B10" t="str">
-        <v>CONFLICT</v>
-      </c>
-      <c r="C10" t="str">
-        <v>家校冲突</v>
-      </c>
-      <c r="D10" t="str">
-        <v>q4</v>
-      </c>
-      <c r="E10" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F10" t="str">
-        <v>1</v>
-      </c>
-      <c r="G10" t="str">
-        <v>评估家校冲突的频率和强度</v>
-      </c>
-      <c r="H10" t="str">
-        <v>&gt;=4 分：冲突频发</v>
-      </c>
-      <c r="I10" t="str">
-        <v>&lt;=2 分：关系和谐</v>
-      </c>
-      <c r="J10" t="str">
-        <v>2.2</v>
-      </c>
-      <c r="K10" t="str">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>HS_QUICK</v>
-      </c>
-      <c r="B11" t="str">
-        <v>SUPPORT</v>
-      </c>
-      <c r="C11" t="str">
-        <v>家庭支持</v>
-      </c>
-      <c r="D11" t="str">
-        <v>q5</v>
-      </c>
-      <c r="E11" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F11" t="str">
-        <v>1</v>
-      </c>
-      <c r="G11" t="str">
-        <v>评估家庭对学生学习的支持程度</v>
-      </c>
-      <c r="H11" t="str">
-        <v>&gt;=4 分：支持充分</v>
-      </c>
-      <c r="I11" t="str">
-        <v>&lt;=2 分：支持不足</v>
-      </c>
-      <c r="J11" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="K11" t="str">
-        <v>0.9</v>
+        <v>有较好的信任基础</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/home_school/assessment.xlsx
+++ b/business-libraries/test-data/home_school/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:V3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,21 +437,36 @@
         <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
+        <v>量表角色*</v>
+      </c>
+      <c r="M1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="N1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="O1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="P1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="Q1" t="str">
         <v>结果可见性*</v>
       </c>
-      <c r="M1" t="str">
+      <c r="R1" t="str">
         <v>数据敏感级*</v>
       </c>
-      <c r="N1" t="str">
+      <c r="S1" t="str">
         <v>来源属性*</v>
       </c>
-      <c r="O1" t="str">
+      <c r="T1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="P1" t="str">
+      <c r="U1" t="str">
         <v>版本*</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="V1" t="str">
         <v>量表说明</v>
       </c>
     </row>
@@ -490,21 +505,36 @@
         <v>5</v>
       </c>
       <c r="L2" t="str">
+        <v>入口筛查</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="M2" t="str">
+      <c r="R2" t="str">
         <v>sensitive</v>
       </c>
-      <c r="N2" t="str">
+      <c r="S2" t="str">
         <v>proprietary</v>
       </c>
-      <c r="O2" t="str">
+      <c r="T2" t="str">
         <v>家校沟通合作手册v1</v>
       </c>
-      <c r="P2" t="str">
+      <c r="U2" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="V2" t="str">
         <v>判断家长配合度、沟通态度和当前关系容器。反向计分：得分越高表示状况越差。</v>
       </c>
     </row>
@@ -543,27 +573,42 @@
         <v>6</v>
       </c>
       <c r="L3" t="str">
+        <v>深度诊断</v>
+      </c>
+      <c r="M3" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>量表[HS_QUICK].维度[HS_ATTITUDE] &gt;= 3 或 量表[HS_QUICK].均分 &gt;= 3.2</v>
+      </c>
+      <c r="P3" t="str">
+        <v>沟通态度维度偏高时才需要判断家长类型，否则不用做</v>
+      </c>
+      <c r="Q3" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="M3" t="str">
+      <c r="R3" t="str">
         <v>sensitive</v>
       </c>
-      <c r="N3" t="str">
+      <c r="S3" t="str">
         <v>proprietary</v>
       </c>
-      <c r="O3" t="str">
+      <c r="T3" t="str">
         <v>家校沟通合作手册v1</v>
       </c>
-      <c r="P3" t="str">
+      <c r="U3" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="V3" t="str">
         <v>在双维速查提示需要重点沟通后使用，用于判断家长互动模式并匹配沟通策略。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/test-data/home_school/assessment.xlsx
+++ b/business-libraries/test-data/home_school/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:AL3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,55 +419,103 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
+        <v>适用年级</v>
+      </c>
+      <c r="G1" t="str">
+        <v>适用学科</v>
+      </c>
+      <c r="H1" t="str">
         <v>施测对象*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>施测形式*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>触发方式*</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>作答频次*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>是否必做*</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>预计用时分钟*</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>作答时限分钟</v>
+      </c>
+      <c r="O1" t="str">
+        <v>最低题数</v>
+      </c>
+      <c r="P1" t="str">
+        <v>使用时机</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>重评间隔天数</v>
+      </c>
+      <c r="R1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="S1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="T1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="U1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="V1" t="str">
+        <v>结果可见性*</v>
+      </c>
+      <c r="W1" t="str">
+        <v>责任角色</v>
+      </c>
+      <c r="X1" t="str">
+        <v>数据敏感级*</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>来源属性*</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>外部授权说明</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>手册出处*</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>版本*</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>量表说明</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>常模参照</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>信度说明</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>效度说明</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>适用前提</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>不适合情况</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>后续建议动作</v>
+      </c>
+      <c r="AK1" t="str">
         <v>量表角色*</v>
       </c>
-      <c r="M1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="N1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="O1" t="str">
-        <v>触发条件</v>
-      </c>
-      <c r="P1" t="str">
-        <v>触发条件说明</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="R1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="S1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="T1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="V1" t="str">
-        <v>量表说明</v>
+      <c r="AL1" t="str">
+        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
@@ -487,55 +535,103 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>teacher</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>self_report</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>manual</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>per_case</v>
       </c>
-      <c r="J2" t="str">
-        <v>是</v>
-      </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
+        <v>是</v>
+      </c>
+      <c r="M2" t="str">
         <v>5</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>判断家长配合度、沟通态度和当前关系容器。反向计分：得分越高表示状况越差。</v>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
         <v>入口筛查</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T2" t="str">
-        <v>家校沟通合作手册v1</v>
-      </c>
-      <c r="U2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V2" t="str">
-        <v>判断家长配合度、沟通态度和当前关系容器。反向计分：得分越高表示状况越差。</v>
+      <c r="AL2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -555,67 +651,115 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>teacher</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>self_report</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>manual</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>per_case</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>否</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>6</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>HS_QUICK</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>量表[HS_QUICK].维度[HS_ATTITUDE] &gt;= 3 或 量表[HS_QUICK].均分 &gt;= 3.2</v>
+      </c>
+      <c r="U3" t="str">
+        <v>沟通态度维度偏高时才需要判断家长类型，否则不用做</v>
+      </c>
+      <c r="V3" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v>家校沟通合作手册v1</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>在双维速查提示需要重点沟通后使用，用于判断家长互动模式并匹配沟通策略。</v>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
         <v>深度诊断</v>
       </c>
-      <c r="M3" t="str">
-        <v>HS_QUICK</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v>量表[HS_QUICK].维度[HS_ATTITUDE] &gt;= 3 或 量表[HS_QUICK].均分 &gt;= 3.2</v>
-      </c>
-      <c r="P3" t="str">
-        <v>沟通态度维度偏高时才需要判断家长类型，否则不用做</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R3" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T3" t="str">
-        <v>家校沟通合作手册v1</v>
-      </c>
-      <c r="U3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V3" t="str">
-        <v>在双维速查提示需要重点沟通后使用，用于判断家长互动模式并匹配沟通策略。</v>
+      <c r="AL3" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:P16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -631,22 +775,40 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
+        <v>子维度</v>
+      </c>
+      <c r="F1" t="str">
         <v>题干*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>题干举例</v>
+      </c>
+      <c r="H1" t="str">
         <v>选项组编码*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>反向计分*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>权重</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>是否必答*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>显示条件</v>
+      </c>
+      <c r="M1" t="str">
         <v>数据用途*</v>
+      </c>
+      <c r="N1" t="str">
+        <v>答题提示</v>
+      </c>
+      <c r="O1" t="str">
+        <v>题目说明</v>
+      </c>
+      <c r="P1" t="str">
+        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
@@ -663,22 +825,40 @@
         <v>配合度</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>家长能够及时回应学校的重要沟通。</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G2" t="str">
-        <v>是</v>
-      </c>
-      <c r="H2" t="str">
-        <v>1</v>
-      </c>
       <c r="I2" t="str">
         <v>是</v>
       </c>
       <c r="J2" t="str">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>是</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>compute</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -695,22 +875,40 @@
         <v>配合度</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>家长愿意共同讨论并执行已经达成的行动。</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G3" t="str">
-        <v>是</v>
-      </c>
-      <c r="H3" t="str">
-        <v>1</v>
-      </c>
       <c r="I3" t="str">
         <v>是</v>
       </c>
       <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
+        <v>是</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>compute</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -727,22 +925,40 @@
         <v>配合度</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>出现分歧后，家长仍愿意继续保持沟通。</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G4" t="str">
-        <v>是</v>
-      </c>
-      <c r="H4" t="str">
-        <v>1</v>
-      </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>是</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>compute</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -759,22 +975,40 @@
         <v>沟通态度</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>家长表达不满时仍能保持基本尊重。</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G5" t="str">
-        <v>是</v>
-      </c>
-      <c r="H5" t="str">
-        <v>1</v>
-      </c>
       <c r="I5" t="str">
         <v>是</v>
       </c>
       <c r="J5" t="str">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v>是</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>compute</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -791,22 +1025,40 @@
         <v>沟通态度</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>家长能够区分事实、推测和情绪。</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G6" t="str">
-        <v>是</v>
-      </c>
-      <c r="H6" t="str">
-        <v>1</v>
-      </c>
       <c r="I6" t="str">
         <v>是</v>
       </c>
       <c r="J6" t="str">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>是</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>compute</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -823,22 +1075,40 @@
         <v>沟通态度</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>家长没有出现威胁、公开抹黑或恶意维权行为。</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G7" t="str">
-        <v>是</v>
-      </c>
-      <c r="H7" t="str">
-        <v>1</v>
-      </c>
       <c r="I7" t="str">
         <v>是</v>
       </c>
       <c r="J7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>是</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>compute</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -855,22 +1125,40 @@
         <v>关系容器</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>目前的关系可以承受一次坦诚而具体的讨论。</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G8" t="str">
-        <v>是</v>
-      </c>
-      <c r="H8" t="str">
-        <v>1</v>
-      </c>
       <c r="I8" t="str">
         <v>是</v>
       </c>
       <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>是</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>compute</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -887,22 +1175,40 @@
         <v>关系容器</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>双方能够在情绪出现时暂停并回到问题解决。</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G9" t="str">
-        <v>是</v>
-      </c>
-      <c r="H9" t="str">
-        <v>1</v>
-      </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>是</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>compute</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -919,22 +1225,40 @@
         <v>关系容器</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>过去的积极沟通经验仍能成为当前关系资源。</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G10" t="str">
-        <v>是</v>
-      </c>
-      <c r="H10" t="str">
-        <v>1</v>
-      </c>
       <c r="I10" t="str">
         <v>是</v>
       </c>
       <c r="J10" t="str">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>是</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>compute</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -951,22 +1275,40 @@
         <v>焦虑水平</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>家长在沟通中反复确认同一件事。</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G11" t="str">
-        <v>是</v>
-      </c>
-      <c r="H11" t="str">
-        <v>1</v>
-      </c>
       <c r="I11" t="str">
         <v>是</v>
       </c>
       <c r="J11" t="str">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
+        <v>是</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>compute</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -983,22 +1325,40 @@
         <v>焦虑水平</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>家长常在非工作时间发来紧急消息。</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G12" t="str">
-        <v>是</v>
-      </c>
-      <c r="H12" t="str">
-        <v>1</v>
-      </c>
       <c r="I12" t="str">
         <v>是</v>
       </c>
       <c r="J12" t="str">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
+        <v>是</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>compute</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1015,22 +1375,40 @@
         <v>控制倾向</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>家长会具体指定学校应该如何处理。</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G13" t="str">
-        <v>是</v>
-      </c>
-      <c r="H13" t="str">
-        <v>1</v>
-      </c>
       <c r="I13" t="str">
         <v>是</v>
       </c>
       <c r="J13" t="str">
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
+        <v>是</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>compute</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1047,22 +1425,40 @@
         <v>控制倾向</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>家长对学校既有安排提出较多质疑。</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G14" t="str">
-        <v>是</v>
-      </c>
-      <c r="H14" t="str">
-        <v>1</v>
-      </c>
       <c r="I14" t="str">
         <v>是</v>
       </c>
       <c r="J14" t="str">
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
+        <v>是</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>compute</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1079,22 +1475,40 @@
         <v>信任基础</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>家长相信教师是出于孩子利益在做判断。</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G15" t="str">
-        <v>是</v>
-      </c>
-      <c r="H15" t="str">
-        <v>1</v>
-      </c>
       <c r="I15" t="str">
         <v>是</v>
       </c>
       <c r="J15" t="str">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>是</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v>compute</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1111,27 +1525,45 @@
         <v>信任基础</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>过去的沟通中，家长兑现过共同约定。</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G16" t="str">
-        <v>是</v>
-      </c>
-      <c r="H16" t="str">
-        <v>1</v>
-      </c>
       <c r="I16" t="str">
         <v>是</v>
       </c>
       <c r="J16" t="str">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
+        <v>是</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>compute</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1303,7 +1735,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1333,6 +1765,12 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
+      <c r="J1" t="str">
+        <v>常模均值</v>
+      </c>
+      <c r="K1" t="str">
+        <v>常模标准差</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1362,6 +1800,12 @@
       <c r="I2" t="str">
         <v>配合度良好</v>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1391,6 +1835,12 @@
       <c r="I3" t="str">
         <v>沟通态度可控</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1420,6 +1870,12 @@
       <c r="I4" t="str">
         <v>关系容器充足</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1449,6 +1905,12 @@
       <c r="I5" t="str">
         <v>情绪相对平稳</v>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1478,6 +1940,12 @@
       <c r="I6" t="str">
         <v>愿意接受学校专业判断</v>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1507,10 +1975,16 @@
       <c r="I7" t="str">
         <v>有较好的信任基础</v>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/home_school/assessment.xlsx
+++ b/business-libraries/test-data/home_school/assessment.xlsx
@@ -520,13 +520,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>家校沟通双维与容器速查</v>
+        <v>家校沟通六维速查</v>
       </c>
       <c r="C2" t="str">
-        <v>双维速查</v>
+        <v>六维速查</v>
       </c>
       <c r="D2" t="str">
         <v>home_school</v>
@@ -586,7 +586,7 @@
         <v>teacher_only</v>
       </c>
       <c r="W2" t="str">
-        <v/>
+        <v>班主任</v>
       </c>
       <c r="X2" t="str">
         <v>sensitive</v>
@@ -601,10 +601,10 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AB2" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AC2" t="str">
-        <v>判断家长配合度、沟通态度和当前关系容器。反向计分：得分越高表示状况越差。</v>
+        <v>按六维度框架判断家校沟通状态：沟通质量、参与效能、教育一致性、角色边界（信任关系与危机响应由深度评估承接）。反向计分：得分越高表示状况越差。</v>
       </c>
       <c r="AD2" t="str">
         <v/>
@@ -631,12 +631,12 @@
         <v>入口筛查</v>
       </c>
       <c r="AL2" t="str">
-        <v/>
+        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="B3" t="str">
         <v>家长分型与沟通策略评估</v>
@@ -687,22 +687,22 @@
         <v/>
       </c>
       <c r="R3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="S3" t="str">
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>量表[HS_QUICK].维度[HS_ATTITUDE] &gt;= 3 或 量表[HS_QUICK].均分 &gt;= 3.2</v>
+        <v>量表[HS_S1].维度[HS_S1D4] &gt;= 3 或 量表[HS_S1].均分 &gt;= 3.2</v>
       </c>
       <c r="U3" t="str">
-        <v>沟通态度维度偏高时才需要判断家长类型，否则不用做</v>
+        <v>沟通质量维度偏高时才需要判断家长类型，否则不用做</v>
       </c>
       <c r="V3" t="str">
         <v>teacher_only</v>
       </c>
       <c r="W3" t="str">
-        <v/>
+        <v>班主任</v>
       </c>
       <c r="X3" t="str">
         <v>sensitive</v>
@@ -717,10 +717,10 @@
         <v>家校沟通合作手册v1</v>
       </c>
       <c r="AB3" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AC3" t="str">
-        <v>在双维速查提示需要重点沟通后使用，用于判断家长互动模式并匹配沟通策略。</v>
+        <v>沟通质量维度偏高时才需要判断家长类型，否则不用做</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -747,7 +747,7 @@
         <v>深度诊断</v>
       </c>
       <c r="AL3" t="str">
-        <v/>
+        <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
   </sheetData>
@@ -813,16 +813,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>coop1</v>
+        <v>q1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>配合度</v>
+        <v>参与效能</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -863,16 +863,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>coop2</v>
+        <v>q2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
       </c>
       <c r="D3" t="str">
-        <v>配合度</v>
+        <v>教育一致性</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -913,16 +913,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>coop3</v>
+        <v>q3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
       </c>
       <c r="D4" t="str">
-        <v>配合度</v>
+        <v>角色边界</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -963,16 +963,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>att1</v>
+        <v>q4</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>沟通态度</v>
+        <v>沟通质量</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -1013,16 +1013,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>att2</v>
+        <v>q5</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>沟通态度</v>
+        <v>沟通质量</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -1063,16 +1063,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B7" t="str">
-        <v>att3</v>
+        <v>q6</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>沟通态度</v>
+        <v>沟通质量</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -1113,16 +1113,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B8" t="str">
-        <v>con1</v>
+        <v>q7</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>关系容器</v>
+        <v>角色边界</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -1163,16 +1163,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B9" t="str">
-        <v>con2</v>
+        <v>q8</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>关系容器</v>
+        <v>角色边界</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -1213,16 +1213,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B10" t="str">
-        <v>con3</v>
+        <v>q9</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>关系容器</v>
+        <v>角色边界</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -1263,10 +1263,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="B11" t="str">
-        <v>p1</v>
+        <v>q1</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="B12" t="str">
-        <v>p2</v>
+        <v>q2</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="B13" t="str">
-        <v>p3</v>
+        <v>q3</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="B14" t="str">
-        <v>p4</v>
+        <v>q4</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1463,16 +1463,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="B15" t="str">
-        <v>p5</v>
+        <v>q5</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
       </c>
       <c r="D15" t="str">
-        <v>信任基础</v>
+        <v>信任关系</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -1513,16 +1513,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="B16" t="str">
-        <v>p6</v>
+        <v>q6</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
       </c>
       <c r="D16" t="str">
-        <v>信任基础</v>
+        <v>信任关系</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1570,7 +1570,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1588,13 +1588,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>几乎没有</v>
+        <v>完全不符合</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1602,13 +1602,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>很少</v>
+        <v>比较不符合</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1616,13 +1616,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>有时</v>
+        <v>一般</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1630,13 +1630,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>经常</v>
+        <v>比较符合</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1644,98 +1644,28 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>几乎每天</v>
+        <v>非常符合</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B7" t="str">
-        <v>1</v>
-      </c>
-      <c r="C7" t="str">
-        <v>完全不符合</v>
-      </c>
-      <c r="D7" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2</v>
-      </c>
-      <c r="C8" t="str">
-        <v>比较不符合</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B9" t="str">
-        <v>3</v>
-      </c>
-      <c r="C9" t="str">
-        <v>一般</v>
-      </c>
-      <c r="D9" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B10" t="str">
-        <v>4</v>
-      </c>
-      <c r="C10" t="str">
-        <v>比较符合</v>
-      </c>
-      <c r="D10" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B11" t="str">
-        <v>5</v>
-      </c>
-      <c r="C11" t="str">
-        <v>非常符合</v>
-      </c>
-      <c r="D11" t="str">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1774,16 +1704,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>HS_COOP</v>
+        <v>HS_S1D1</v>
       </c>
       <c r="C2" t="str">
-        <v>配合度</v>
+        <v>参与效能</v>
       </c>
       <c r="D2" t="str">
-        <v>coop1,coop2,coop3</v>
+        <v>q1</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1792,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>配合度维度</v>
+        <v>参与效能维度</v>
       </c>
       <c r="H2" t="str">
         <v>家长回应慢、不参与共同行动</v>
       </c>
       <c r="I2" t="str">
-        <v>配合度良好</v>
+        <v>参与效能良好</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -1809,16 +1739,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>HS_ATTITUDE</v>
+        <v>HS_S1D2</v>
       </c>
       <c r="C3" t="str">
-        <v>沟通态度</v>
+        <v>教育一致性</v>
       </c>
       <c r="D3" t="str">
-        <v>att1,att2,att3</v>
+        <v>q2</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1827,13 +1757,13 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>沟通态度维度</v>
+        <v>教育一致性维度</v>
       </c>
       <c r="H3" t="str">
-        <v>出现不尊重、混淆事实与情绪甚至威胁行为</v>
+        <v>家长不认同或不愿执行共同达成的教育行动</v>
       </c>
       <c r="I3" t="str">
-        <v>沟通态度可控</v>
+        <v>教育方向一致</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -1844,16 +1774,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>HS_CONTAINER</v>
+        <v>HS_S1D3</v>
       </c>
       <c r="C4" t="str">
-        <v>关系容器</v>
+        <v>角色边界</v>
       </c>
       <c r="D4" t="str">
-        <v>con1,con2,con3</v>
+        <v>q3,q7,q8,q9</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1862,13 +1792,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>关系容器维度</v>
+        <v>角色边界维度</v>
       </c>
       <c r="H4" t="str">
-        <v>关系无法承受坦诚讨论</v>
+        <v>关系无法承受坦诚讨论，边界模糊</v>
       </c>
       <c r="I4" t="str">
-        <v>关系容器充足</v>
+        <v>角色边界清晰、角色边界充足</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -1879,16 +1809,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>HS_ANXIETY</v>
+        <v>HS_S1D4</v>
       </c>
       <c r="C5" t="str">
-        <v>焦虑水平</v>
+        <v>沟通质量</v>
       </c>
       <c r="D5" t="str">
-        <v>p1,p2</v>
+        <v>q4,q5,q6</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1897,13 +1827,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>焦虑水平维度</v>
+        <v>沟通质量维度</v>
       </c>
       <c r="H5" t="str">
-        <v>家长处于高焦虑，难以接收复杂信息</v>
+        <v>出现不尊重、混淆事实与情绪甚至威胁行为</v>
       </c>
       <c r="I5" t="str">
-        <v>情绪相对平稳</v>
+        <v>沟通质量可控</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -1914,16 +1844,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="B6" t="str">
-        <v>HS_CONTROL</v>
+        <v>HS_S2D1</v>
       </c>
       <c r="C6" t="str">
-        <v>控制倾向</v>
+        <v>焦虑水平</v>
       </c>
       <c r="D6" t="str">
-        <v>p3,p4</v>
+        <v>q1,q2</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1932,13 +1862,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>控制倾向维度</v>
+        <v>焦虑水平维度</v>
       </c>
       <c r="H6" t="str">
-        <v>家长倾向于主导教育方式并质疑学校安排</v>
+        <v>家长处于高焦虑，难以接收复杂信息</v>
       </c>
       <c r="I6" t="str">
-        <v>愿意接受学校专业判断</v>
+        <v>情绪相对平稳</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1949,16 +1879,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>HS_TRUST</v>
+        <v>HS_S2D2</v>
       </c>
       <c r="C7" t="str">
-        <v>信任基础</v>
+        <v>控制倾向</v>
       </c>
       <c r="D7" t="str">
-        <v>p5,p6</v>
+        <v>q3,q4</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1967,24 +1897,59 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>信任基础维度</v>
+        <v>控制倾向维度</v>
       </c>
       <c r="H7" t="str">
+        <v>家长倾向于主导教育方式并质疑学校安排</v>
+      </c>
+      <c r="I7" t="str">
+        <v>愿意接受学校专业判断</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HS_S2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>HS_S2D3</v>
+      </c>
+      <c r="C8" t="str">
+        <v>信任关系</v>
+      </c>
+      <c r="D8" t="str">
+        <v>q5,q6</v>
+      </c>
+      <c r="E8" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F8" t="str">
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
+        <v>信任关系维度</v>
+      </c>
+      <c r="H8" t="str">
         <v>对学校缺乏基本信任</v>
       </c>
-      <c r="I7" t="str">
-        <v>有较好的信任基础</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
+      <c r="I8" t="str">
+        <v>有较好的信任关系</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/home_school/assessment.xlsx
+++ b/business-libraries/test-data/home_school/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:V3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,114 +419,66 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
-        <v>适用年级</v>
+        <v>施测对象*</v>
       </c>
       <c r="G1" t="str">
-        <v>适用学科</v>
+        <v>施测形式*</v>
       </c>
       <c r="H1" t="str">
-        <v>施测对象*</v>
+        <v>触发方式*</v>
       </c>
       <c r="I1" t="str">
-        <v>施测形式*</v>
+        <v>作答频次*</v>
       </c>
       <c r="J1" t="str">
-        <v>触发方式*</v>
+        <v>是否必做*</v>
       </c>
       <c r="K1" t="str">
-        <v>作答频次*</v>
+        <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
-        <v>是否必做*</v>
+        <v>量表角色*</v>
       </c>
       <c r="M1" t="str">
-        <v>预计用时分钟*</v>
+        <v>前置量表编码</v>
       </c>
       <c r="N1" t="str">
-        <v>作答时限分钟</v>
+        <v>互斥量表编码</v>
       </c>
       <c r="O1" t="str">
-        <v>最低题数</v>
+        <v>触发条件</v>
       </c>
       <c r="P1" t="str">
-        <v>使用时机</v>
+        <v>触发条件说明</v>
       </c>
       <c r="Q1" t="str">
-        <v>重评间隔天数</v>
+        <v>结果可见性*</v>
       </c>
       <c r="R1" t="str">
-        <v>前置量表编码</v>
+        <v>数据敏感级*</v>
       </c>
       <c r="S1" t="str">
-        <v>互斥量表编码</v>
+        <v>来源属性*</v>
       </c>
       <c r="T1" t="str">
-        <v>触发条件</v>
+        <v>手册出处*</v>
       </c>
       <c r="U1" t="str">
-        <v>触发条件说明</v>
+        <v>版本*</v>
       </c>
       <c r="V1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="W1" t="str">
-        <v>责任角色</v>
-      </c>
-      <c r="X1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>外部授权说明</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="AC1" t="str">
         <v>量表说明</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>常模参照</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>信度说明</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>效度说明</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>隐私声明</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>适用前提</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>不适合情况</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>后续建议动作</v>
-      </c>
-      <c r="AK1" t="str">
-        <v>量表角色*</v>
-      </c>
-      <c r="AL1" t="str">
-        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B2" t="str">
-        <v>家校沟通六维速查</v>
+        <v>家校沟通双维与容器速查</v>
       </c>
       <c r="C2" t="str">
-        <v>六维速查</v>
+        <v>双维速查</v>
       </c>
       <c r="D2" t="str">
         <v>home_school</v>
@@ -535,28 +487,28 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="G2" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="H2" t="str">
+        <v>manual</v>
+      </c>
+      <c r="I2" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="J2" t="str">
+        <v>是</v>
+      </c>
+      <c r="K2" t="str">
+        <v>5</v>
+      </c>
+      <c r="L2" t="str">
+        <v>入口筛查</v>
+      </c>
+      <c r="M2" t="str">
         <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v>teacher</v>
-      </c>
-      <c r="I2" t="str">
-        <v>self_report</v>
-      </c>
-      <c r="J2" t="str">
-        <v>manual</v>
-      </c>
-      <c r="K2" t="str">
-        <v>per_case</v>
-      </c>
-      <c r="L2" t="str">
-        <v>是</v>
-      </c>
-      <c r="M2" t="str">
-        <v>5</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -568,75 +520,27 @@
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>teacher_only</v>
       </c>
       <c r="R2" t="str">
-        <v/>
+        <v>sensitive</v>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>家校沟通合作手册v1</v>
       </c>
       <c r="U2" t="str">
-        <v/>
+        <v>1.0.0</v>
       </c>
       <c r="V2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="W2" t="str">
-        <v>班主任</v>
-      </c>
-      <c r="X2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="Y2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="Z2" t="str">
-        <v/>
-      </c>
-      <c r="AA2" t="str">
-        <v>家校沟通合作手册v1</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>4.0.0</v>
-      </c>
-      <c r="AC2" t="str">
-        <v>按六维度框架判断家校沟通状态：沟通质量、参与效能、教育一致性、角色边界（信任关系与危机响应由深度评估承接）。反向计分：得分越高表示状况越差。</v>
-      </c>
-      <c r="AD2" t="str">
-        <v/>
-      </c>
-      <c r="AE2" t="str">
-        <v/>
-      </c>
-      <c r="AF2" t="str">
-        <v/>
-      </c>
-      <c r="AG2" t="str">
-        <v/>
-      </c>
-      <c r="AH2" t="str">
-        <v/>
-      </c>
-      <c r="AI2" t="str">
-        <v/>
-      </c>
-      <c r="AJ2" t="str">
-        <v/>
-      </c>
-      <c r="AK2" t="str">
-        <v>入口筛查</v>
-      </c>
-      <c r="AL2" t="str">
-        <v>决定要不要往下做深度诊断</v>
+        <v>判断家长配合度、沟通态度和当前关系容器。反向计分：得分越高表示状况越差。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B3" t="str">
         <v>家长分型与沟通策略评估</v>
@@ -651,115 +555,67 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H3" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I3" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J3" t="str">
-        <v>manual</v>
+        <v>否</v>
       </c>
       <c r="K3" t="str">
-        <v>per_case</v>
+        <v>6</v>
       </c>
       <c r="L3" t="str">
-        <v>否</v>
+        <v>深度诊断</v>
       </c>
       <c r="M3" t="str">
-        <v>6</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="N3" t="str">
         <v/>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>量表[HS_QUICK].维度[HS_ATTITUDE] &gt;= 3 或 量表[HS_QUICK].均分 &gt;= 3.2</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>沟通态度维度偏高时才需要判断家长类型，否则不用做</v>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>teacher_only</v>
       </c>
       <c r="R3" t="str">
-        <v>HS_S1</v>
+        <v>sensitive</v>
       </c>
       <c r="S3" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="T3" t="str">
-        <v>量表[HS_S1].维度[HS_S1D4] &gt;= 3 或 量表[HS_S1].均分 &gt;= 3.2</v>
+        <v>家校沟通合作手册v1</v>
       </c>
       <c r="U3" t="str">
-        <v>沟通质量维度偏高时才需要判断家长类型，否则不用做</v>
+        <v>1.0.0</v>
       </c>
       <c r="V3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="W3" t="str">
-        <v>班主任</v>
-      </c>
-      <c r="X3" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="Y3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="Z3" t="str">
-        <v/>
-      </c>
-      <c r="AA3" t="str">
-        <v>家校沟通合作手册v1</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>4.0.0</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>沟通质量维度偏高时才需要判断家长类型，否则不用做</v>
-      </c>
-      <c r="AD3" t="str">
-        <v/>
-      </c>
-      <c r="AE3" t="str">
-        <v/>
-      </c>
-      <c r="AF3" t="str">
-        <v/>
-      </c>
-      <c r="AG3" t="str">
-        <v/>
-      </c>
-      <c r="AH3" t="str">
-        <v/>
-      </c>
-      <c r="AI3" t="str">
-        <v/>
-      </c>
-      <c r="AJ3" t="str">
-        <v/>
-      </c>
-      <c r="AK3" t="str">
-        <v>深度诊断</v>
-      </c>
-      <c r="AL3" t="str">
-        <v>定位薄弱维度，匹配对应工具</v>
+        <v>在双维速查提示需要重点沟通后使用，用于判断家长互动模式并匹配沟通策略。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:J16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -775,498 +631,318 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
-        <v>子维度</v>
+        <v>题干*</v>
       </c>
       <c r="F1" t="str">
-        <v>题干*</v>
+        <v>选项组编码*</v>
       </c>
       <c r="G1" t="str">
-        <v>题干举例</v>
+        <v>反向计分*</v>
       </c>
       <c r="H1" t="str">
-        <v>选项组编码*</v>
+        <v>权重</v>
       </c>
       <c r="I1" t="str">
-        <v>反向计分*</v>
+        <v>是否必答*</v>
       </c>
       <c r="J1" t="str">
-        <v>权重</v>
-      </c>
-      <c r="K1" t="str">
-        <v>是否必答*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>显示条件</v>
-      </c>
-      <c r="M1" t="str">
         <v>数据用途*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>答题提示</v>
-      </c>
-      <c r="O1" t="str">
-        <v>题目说明</v>
-      </c>
-      <c r="P1" t="str">
-        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B2" t="str">
-        <v>q1</v>
+        <v>coop1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>参与效能</v>
+        <v>配合度</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>家长能够及时回应学校的重要沟通。</v>
       </c>
       <c r="F2" t="str">
-        <v>家长能够及时回应学校的重要沟通。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H2" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="str">
         <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>1</v>
-      </c>
-      <c r="K2" t="str">
-        <v>是</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
         <v>compute</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B3" t="str">
-        <v>q2</v>
+        <v>coop2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
       </c>
       <c r="D3" t="str">
-        <v>教育一致性</v>
+        <v>配合度</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>家长愿意共同讨论并执行已经达成的行动。</v>
       </c>
       <c r="F3" t="str">
-        <v>家长愿意共同讨论并执行已经达成的行动。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H3" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="str">
         <v>是</v>
       </c>
       <c r="J3" t="str">
-        <v>1</v>
-      </c>
-      <c r="K3" t="str">
-        <v>是</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
         <v>compute</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B4" t="str">
-        <v>q3</v>
+        <v>coop3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
       </c>
       <c r="D4" t="str">
-        <v>角色边界</v>
+        <v>配合度</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>出现分歧后，家长仍愿意继续保持沟通。</v>
       </c>
       <c r="F4" t="str">
-        <v>出现分歧后，家长仍愿意继续保持沟通。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H4" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
-        <v>1</v>
-      </c>
-      <c r="K4" t="str">
-        <v>是</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
         <v>compute</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B5" t="str">
-        <v>q4</v>
+        <v>att1</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>沟通质量</v>
+        <v>沟通态度</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>家长表达不满时仍能保持基本尊重。</v>
       </c>
       <c r="F5" t="str">
-        <v>家长表达不满时仍能保持基本尊重。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H5" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="str">
         <v>是</v>
       </c>
       <c r="J5" t="str">
-        <v>1</v>
-      </c>
-      <c r="K5" t="str">
-        <v>是</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
         <v>compute</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B6" t="str">
-        <v>q5</v>
+        <v>att2</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>沟通质量</v>
+        <v>沟通态度</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>家长能够区分事实、推测和情绪。</v>
       </c>
       <c r="F6" t="str">
-        <v>家长能够区分事实、推测和情绪。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H6" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="str">
         <v>是</v>
       </c>
       <c r="J6" t="str">
-        <v>1</v>
-      </c>
-      <c r="K6" t="str">
-        <v>是</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
         <v>compute</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B7" t="str">
-        <v>q6</v>
+        <v>att3</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>沟通质量</v>
+        <v>沟通态度</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>家长没有出现威胁、公开抹黑或恶意维权行为。</v>
       </c>
       <c r="F7" t="str">
-        <v>家长没有出现威胁、公开抹黑或恶意维权行为。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H7" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="str">
         <v>是</v>
       </c>
       <c r="J7" t="str">
-        <v>1</v>
-      </c>
-      <c r="K7" t="str">
-        <v>是</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
         <v>compute</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B8" t="str">
-        <v>q7</v>
+        <v>con1</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>角色边界</v>
+        <v>关系容器</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>目前的关系可以承受一次坦诚而具体的讨论。</v>
       </c>
       <c r="F8" t="str">
-        <v>目前的关系可以承受一次坦诚而具体的讨论。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H8" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
         <v>是</v>
       </c>
       <c r="J8" t="str">
-        <v>1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>是</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
         <v>compute</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B9" t="str">
-        <v>q8</v>
+        <v>con2</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>角色边界</v>
+        <v>关系容器</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>双方能够在情绪出现时暂停并回到问题解决。</v>
       </c>
       <c r="F9" t="str">
-        <v>双方能够在情绪出现时暂停并回到问题解决。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H9" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
-        <v>1</v>
-      </c>
-      <c r="K9" t="str">
-        <v>是</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
         <v>compute</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B10" t="str">
-        <v>q9</v>
+        <v>con3</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>角色边界</v>
+        <v>关系容器</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>过去的积极沟通经验仍能成为当前关系资源。</v>
       </c>
       <c r="F10" t="str">
-        <v>过去的积极沟通经验仍能成为当前关系资源。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H10" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="str">
         <v>是</v>
       </c>
       <c r="J10" t="str">
-        <v>1</v>
-      </c>
-      <c r="K10" t="str">
-        <v>是</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
         <v>compute</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B11" t="str">
-        <v>q1</v>
+        <v>p1</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
@@ -1275,48 +951,30 @@
         <v>焦虑水平</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>家长在沟通中反复确认同一件事。</v>
       </c>
       <c r="F11" t="str">
-        <v>家长在沟通中反复确认同一件事。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H11" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="str">
         <v>是</v>
       </c>
       <c r="J11" t="str">
-        <v>1</v>
-      </c>
-      <c r="K11" t="str">
-        <v>是</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
         <v>compute</v>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B12" t="str">
-        <v>q2</v>
+        <v>p2</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
@@ -1325,48 +983,30 @@
         <v>焦虑水平</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>家长常在非工作时间发来紧急消息。</v>
       </c>
       <c r="F12" t="str">
-        <v>家长常在非工作时间发来紧急消息。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H12" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I12" t="str">
         <v>是</v>
       </c>
       <c r="J12" t="str">
-        <v>1</v>
-      </c>
-      <c r="K12" t="str">
-        <v>是</v>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
         <v>compute</v>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B13" t="str">
-        <v>q3</v>
+        <v>p3</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
@@ -1375,48 +1015,30 @@
         <v>控制倾向</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>家长会具体指定学校应该如何处理。</v>
       </c>
       <c r="F13" t="str">
-        <v>家长会具体指定学校应该如何处理。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H13" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I13" t="str">
         <v>是</v>
       </c>
       <c r="J13" t="str">
-        <v>1</v>
-      </c>
-      <c r="K13" t="str">
-        <v>是</v>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
         <v>compute</v>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B14" t="str">
-        <v>q4</v>
+        <v>p4</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1425,152 +1047,98 @@
         <v>控制倾向</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>家长对学校既有安排提出较多质疑。</v>
       </c>
       <c r="F14" t="str">
-        <v>家长对学校既有安排提出较多质疑。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H14" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I14" t="str">
         <v>是</v>
       </c>
       <c r="J14" t="str">
-        <v>1</v>
-      </c>
-      <c r="K14" t="str">
-        <v>是</v>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
         <v>compute</v>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-      <c r="P14" t="str">
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B15" t="str">
-        <v>q5</v>
+        <v>p5</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
       </c>
       <c r="D15" t="str">
-        <v>信任关系</v>
+        <v>信任基础</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>家长相信教师是出于孩子利益在做判断。</v>
       </c>
       <c r="F15" t="str">
-        <v>家长相信教师是出于孩子利益在做判断。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H15" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I15" t="str">
         <v>是</v>
       </c>
       <c r="J15" t="str">
-        <v>1</v>
-      </c>
-      <c r="K15" t="str">
-        <v>是</v>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
         <v>compute</v>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B16" t="str">
-        <v>q6</v>
+        <v>p6</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
       </c>
       <c r="D16" t="str">
-        <v>信任关系</v>
+        <v>信任基础</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>过去的沟通中，家长兑现过共同约定。</v>
       </c>
       <c r="F16" t="str">
-        <v>过去的沟通中，家长兑现过共同约定。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>是</v>
       </c>
       <c r="H16" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I16" t="str">
         <v>是</v>
       </c>
       <c r="J16" t="str">
-        <v>1</v>
-      </c>
-      <c r="K16" t="str">
-        <v>是</v>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
         <v>compute</v>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-      <c r="P16" t="str">
-        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1588,13 +1156,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>完全不符合</v>
+        <v>几乎没有</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1602,13 +1170,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>比较不符合</v>
+        <v>很少</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1616,13 +1184,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>一般</v>
+        <v>有时</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1630,13 +1198,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>比较符合</v>
+        <v>经常</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1644,28 +1212,98 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>非常符合</v>
+        <v>几乎每天</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>3</v>
+      </c>
+      <c r="C9" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D9" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>4</v>
+      </c>
+      <c r="C10" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B11" t="str">
+        <v>5</v>
+      </c>
+      <c r="C11" t="str">
+        <v>非常符合</v>
+      </c>
+      <c r="D11" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:I7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1695,25 +1333,19 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
-      <c r="J1" t="str">
-        <v>常模均值</v>
-      </c>
-      <c r="K1" t="str">
-        <v>常模标准差</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B2" t="str">
-        <v>HS_S1D1</v>
+        <v>HS_COOP</v>
       </c>
       <c r="C2" t="str">
-        <v>参与效能</v>
+        <v>配合度</v>
       </c>
       <c r="D2" t="str">
-        <v>q1</v>
+        <v>coop1,coop2,coop3</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1722,33 +1354,27 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>参与效能维度</v>
+        <v>配合度维度</v>
       </c>
       <c r="H2" t="str">
         <v>家长回应慢、不参与共同行动</v>
       </c>
       <c r="I2" t="str">
-        <v>参与效能良好</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
+        <v>配合度良好</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B3" t="str">
-        <v>HS_S1D2</v>
+        <v>HS_ATTITUDE</v>
       </c>
       <c r="C3" t="str">
-        <v>教育一致性</v>
+        <v>沟通态度</v>
       </c>
       <c r="D3" t="str">
-        <v>q2</v>
+        <v>att1,att2,att3</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1757,33 +1383,27 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>教育一致性维度</v>
+        <v>沟通态度维度</v>
       </c>
       <c r="H3" t="str">
-        <v>家长不认同或不愿执行共同达成的教育行动</v>
+        <v>出现不尊重、混淆事实与情绪甚至威胁行为</v>
       </c>
       <c r="I3" t="str">
-        <v>教育方向一致</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
+        <v>沟通态度可控</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_S1</v>
+        <v>HS_QUICK</v>
       </c>
       <c r="B4" t="str">
-        <v>HS_S1D3</v>
+        <v>HS_CONTAINER</v>
       </c>
       <c r="C4" t="str">
-        <v>角色边界</v>
+        <v>关系容器</v>
       </c>
       <c r="D4" t="str">
-        <v>q3,q7,q8,q9</v>
+        <v>con1,con2,con3</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1792,33 +1412,27 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>角色边界维度</v>
+        <v>关系容器维度</v>
       </c>
       <c r="H4" t="str">
-        <v>关系无法承受坦诚讨论，边界模糊</v>
+        <v>关系无法承受坦诚讨论</v>
       </c>
       <c r="I4" t="str">
-        <v>角色边界清晰、角色边界充足</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
+        <v>关系容器充足</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_S1</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B5" t="str">
-        <v>HS_S1D4</v>
+        <v>HS_ANXIETY</v>
       </c>
       <c r="C5" t="str">
-        <v>沟通质量</v>
+        <v>焦虑水平</v>
       </c>
       <c r="D5" t="str">
-        <v>q4,q5,q6</v>
+        <v>p1,p2</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1827,33 +1441,27 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>沟通质量维度</v>
+        <v>焦虑水平维度</v>
       </c>
       <c r="H5" t="str">
-        <v>出现不尊重、混淆事实与情绪甚至威胁行为</v>
+        <v>家长处于高焦虑，难以接收复杂信息</v>
       </c>
       <c r="I5" t="str">
-        <v>沟通质量可控</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
+        <v>情绪相对平稳</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B6" t="str">
-        <v>HS_S2D1</v>
+        <v>HS_CONTROL</v>
       </c>
       <c r="C6" t="str">
-        <v>焦虑水平</v>
+        <v>控制倾向</v>
       </c>
       <c r="D6" t="str">
-        <v>q1,q2</v>
+        <v>p3,p4</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1862,33 +1470,27 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>焦虑水平维度</v>
+        <v>控制倾向维度</v>
       </c>
       <c r="H6" t="str">
-        <v>家长处于高焦虑，难以接收复杂信息</v>
+        <v>家长倾向于主导教育方式并质疑学校安排</v>
       </c>
       <c r="I6" t="str">
-        <v>情绪相对平稳</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
+        <v>愿意接受学校专业判断</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_S2</v>
+        <v>HS_PARENT_TYPE</v>
       </c>
       <c r="B7" t="str">
-        <v>HS_S2D2</v>
+        <v>HS_TRUST</v>
       </c>
       <c r="C7" t="str">
-        <v>控制倾向</v>
+        <v>信任基础</v>
       </c>
       <c r="D7" t="str">
-        <v>q3,q4</v>
+        <v>p5,p6</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1897,59 +1499,18 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>控制倾向维度</v>
+        <v>信任基础维度</v>
       </c>
       <c r="H7" t="str">
-        <v>家长倾向于主导教育方式并质疑学校安排</v>
+        <v>对学校缺乏基本信任</v>
       </c>
       <c r="I7" t="str">
-        <v>愿意接受学校专业判断</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>HS_S2</v>
-      </c>
-      <c r="B8" t="str">
-        <v>HS_S2D3</v>
-      </c>
-      <c r="C8" t="str">
-        <v>信任关系</v>
-      </c>
-      <c r="D8" t="str">
-        <v>q5,q6</v>
-      </c>
-      <c r="E8" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F8" t="str">
-        <v>1</v>
-      </c>
-      <c r="G8" t="str">
-        <v>信任关系维度</v>
-      </c>
-      <c r="H8" t="str">
-        <v>对学校缺乏基本信任</v>
-      </c>
-      <c r="I8" t="str">
-        <v>有较好的信任关系</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
+        <v>有较好的信任基础</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/home_school/assessment.xlsx
+++ b/business-libraries/test-data/home_school/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:AL3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,66 +419,114 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
+        <v>适用年级</v>
+      </c>
+      <c r="G1" t="str">
+        <v>适用学科</v>
+      </c>
+      <c r="H1" t="str">
         <v>施测对象*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>施测形式*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>触发方式*</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>作答频次*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>是否必做*</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>预计用时分钟*</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>作答时限分钟</v>
+      </c>
+      <c r="O1" t="str">
+        <v>最低题数</v>
+      </c>
+      <c r="P1" t="str">
+        <v>使用时机</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>重评间隔天数</v>
+      </c>
+      <c r="R1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="S1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="T1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="U1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="V1" t="str">
+        <v>结果可见性*</v>
+      </c>
+      <c r="W1" t="str">
+        <v>责任角色</v>
+      </c>
+      <c r="X1" t="str">
+        <v>数据敏感级*</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>来源属性*</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>外部授权说明</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>手册出处*</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>版本*</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>量表说明</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>常模参照</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>信度说明</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>效度说明</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>适用前提</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>不适合情况</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>后续建议动作</v>
+      </c>
+      <c r="AK1" t="str">
         <v>量表角色*</v>
       </c>
-      <c r="M1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="N1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="O1" t="str">
-        <v>触发条件</v>
-      </c>
-      <c r="P1" t="str">
-        <v>触发条件说明</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="R1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="S1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="T1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="V1" t="str">
-        <v>量表说明</v>
+      <c r="AL1" t="str">
+        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>家校沟通双维与容器速查</v>
+        <v>家校沟通六维评估</v>
       </c>
       <c r="C2" t="str">
-        <v>双维速查</v>
+        <v>六维评估</v>
       </c>
       <c r="D2" t="str">
         <v>home_school</v>
@@ -487,66 +535,114 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>teacher</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>self_report</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>manual</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>per_case</v>
       </c>
-      <c r="J2" t="str">
-        <v>是</v>
-      </c>
-      <c r="K2" t="str">
-        <v>5</v>
-      </c>
       <c r="L2" t="str">
+        <v>是</v>
+      </c>
+      <c r="M2" t="str">
+        <v>10</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W2" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X2" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>4.2.0</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>面向班主任/年级组的六维诊断评估（评估量表V2.0）：沟通质量、角色边界、教育一致性、信任关系、参与效能、危机响应，每维 5 题共 30 题。正向计分：评分越高=家校关系越健康；常模参考均分 4.0，低于常模需关注。</v>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
         <v>入口筛查</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T2" t="str">
-        <v>家校沟通合作手册v1</v>
-      </c>
-      <c r="U2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V2" t="str">
-        <v>判断家长配合度、沟通态度和当前关系容器。反向计分：得分越高表示状况越差。</v>
+      <c r="AL2" t="str">
+        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S2</v>
       </c>
       <c r="B3" t="str">
-        <v>家长分型与沟通策略评估</v>
+        <v>家校沟通红线检查</v>
       </c>
       <c r="C3" t="str">
-        <v>家长分型</v>
+        <v>红线检查</v>
       </c>
       <c r="D3" t="str">
         <v>home_school</v>
@@ -555,67 +651,115 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>teacher</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>self_report</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>manual</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>per_case</v>
       </c>
-      <c r="J3" t="str">
-        <v>否</v>
-      </c>
-      <c r="K3" t="str">
-        <v>6</v>
-      </c>
       <c r="L3" t="str">
-        <v>深度诊断</v>
+        <v>否</v>
       </c>
       <c r="M3" t="str">
-        <v>HS_QUICK</v>
+        <v>2</v>
       </c>
       <c r="N3" t="str">
         <v/>
       </c>
       <c r="O3" t="str">
-        <v>量表[HS_QUICK].维度[HS_ATTITUDE] &gt;= 3 或 量表[HS_QUICK].均分 &gt;= 3.2</v>
+        <v/>
       </c>
       <c r="P3" t="str">
-        <v>沟通态度维度偏高时才需要判断家长类型，否则不用做</v>
+        <v/>
       </c>
       <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>量表[HS_S1].均分 &lt;= 4</v>
+      </c>
+      <c r="U3" t="str">
+        <v>六维评估均分低于 4.0（出现风险迹象）时建议做红线检查，逐项核对 R 类红线；健康家庭可不做</v>
+      </c>
+      <c r="V3" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="R3" t="str">
+      <c r="W3" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X3" t="str">
         <v>sensitive</v>
       </c>
-      <c r="S3" t="str">
+      <c r="Y3" t="str">
         <v>proprietary</v>
       </c>
-      <c r="T3" t="str">
-        <v>家校沟通合作手册v1</v>
-      </c>
-      <c r="U3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V3" t="str">
-        <v>在双维速查提示需要重点沟通后使用，用于判断家长互动模式并匹配沟通策略。</v>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v>家校沟通与合作test0730-AI入口（评估量表V2.0/归因库/干预方案库/关联关系表）</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>4.2.0</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>按干预方案库 R1-R8 红线清单逐项勾选（否=0/是=1），任一命中即触发五级危机干预熔断：停止常规方案，转危机响应流程。</v>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
+        <v>红线检查</v>
+      </c>
+      <c r="AL3" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:P39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -631,514 +775,1952 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
+        <v>子维度</v>
+      </c>
+      <c r="F1" t="str">
         <v>题干*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>题干举例</v>
+      </c>
+      <c r="H1" t="str">
         <v>选项组编码*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>反向计分*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>权重</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>是否必答*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>显示条件</v>
+      </c>
+      <c r="M1" t="str">
         <v>数据用途*</v>
+      </c>
+      <c r="N1" t="str">
+        <v>答题提示</v>
+      </c>
+      <c r="O1" t="str">
+        <v>题目说明</v>
+      </c>
+      <c r="P1" t="str">
+        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>coop1</v>
+        <v>q1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>配合度</v>
+        <v>沟通质量</v>
       </c>
       <c r="E2" t="str">
-        <v>家长能够及时回应学校的重要沟通。</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>AGREE_5</v>
+        <v>我与这位家长能够顺畅、及时地交流孩子的在校情况</v>
       </c>
       <c r="G2" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I2" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J2" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>是</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>coop2</v>
+        <v>q2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
       </c>
       <c r="D3" t="str">
-        <v>配合度</v>
+        <v>沟通质量</v>
       </c>
       <c r="E3" t="str">
-        <v>家长愿意共同讨论并执行已经达成的行动。</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>AGREE_5</v>
+        <v>这位家长会主动向我反馈孩子在家中的表现与变化</v>
       </c>
       <c r="G3" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I3" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
+        <v>是</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>coop3</v>
+        <v>q3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
       </c>
       <c r="D4" t="str">
-        <v>配合度</v>
+        <v>沟通质量</v>
       </c>
       <c r="E4" t="str">
-        <v>出现分歧后，家长仍愿意继续保持沟通。</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>AGREE_5</v>
+        <v>我与这位家长沟通时氛围轻松，双方都能坦诚表达</v>
       </c>
       <c r="G4" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I4" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J4" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>是</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>att1</v>
+        <v>q4</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>沟通态度</v>
+        <v>沟通质量</v>
       </c>
       <c r="E5" t="str">
-        <v>家长表达不满时仍能保持基本尊重。</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>AGREE_5</v>
+        <v>这位家长能够清晰表达自己对教育的期望与诉求</v>
       </c>
       <c r="G5" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I5" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J5" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v>是</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>att2</v>
+        <v>q5</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>沟通态度</v>
+        <v>沟通质量</v>
       </c>
       <c r="E6" t="str">
-        <v>家长能够区分事实、推测和情绪。</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>AGREE_5</v>
+        <v>当我有重要信息需要传达时，能够确保有效送达并得到确认</v>
       </c>
       <c r="G6" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I6" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>是</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B7" t="str">
-        <v>att3</v>
+        <v>q6</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>沟通态度</v>
+        <v>角色边界</v>
       </c>
       <c r="E7" t="str">
-        <v>家长没有出现威胁、公开抹黑或恶意维权行为。</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>AGREE_5</v>
+        <v>这位家长能在合适的时间联系我，不打扰我的休息与非工作时间</v>
       </c>
       <c r="G7" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I7" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J7" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>是</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B8" t="str">
-        <v>con1</v>
+        <v>q7</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>关系容器</v>
+        <v>角色边界</v>
       </c>
       <c r="E8" t="str">
-        <v>目前的关系可以承受一次坦诚而具体的讨论。</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>AGREE_5</v>
+        <v>这位家长尊重我在教学与班级事务上的专业主导权</v>
       </c>
       <c r="G8" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I8" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J8" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>是</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B9" t="str">
-        <v>con2</v>
+        <v>q8</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>关系容器</v>
+        <v>角色边界</v>
       </c>
       <c r="E9" t="str">
-        <v>双方能够在情绪出现时暂停并回到问题解决。</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>AGREE_5</v>
+        <v>这位家长能把握参与的尺度，不过度介入班级内部事务</v>
       </c>
       <c r="G9" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I9" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J9" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>是</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B10" t="str">
-        <v>con3</v>
+        <v>q9</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>关系容器</v>
+        <v>角色边界</v>
       </c>
       <c r="E10" t="str">
-        <v>过去的积极沟通经验仍能成为当前关系资源。</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>AGREE_5</v>
+        <v>这位家长与我的交往保持恰当的职业距离，不越界</v>
       </c>
       <c r="G10" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I10" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J10" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>是</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="B11" t="str">
-        <v>p1</v>
+        <v>q10</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>焦虑水平</v>
+        <v>角色边界</v>
       </c>
       <c r="E11" t="str">
-        <v>家长在沟通中反复确认同一件事。</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>AGREE_5</v>
+        <v>这位家长理解并配合学校在家长群、家委会等渠道上的规则</v>
       </c>
       <c r="G11" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I11" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J11" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
+        <v>是</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="B12" t="str">
-        <v>p2</v>
+        <v>q11</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
       </c>
       <c r="D12" t="str">
-        <v>焦虑水平</v>
+        <v>教育一致性</v>
       </c>
       <c r="E12" t="str">
-        <v>家长常在非工作时间发来紧急消息。</v>
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v>AGREE_5</v>
+        <v>这位家长认同并接纳学校的教育理念与要求</v>
       </c>
       <c r="G12" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I12" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J12" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
+        <v>是</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="B13" t="str">
-        <v>p3</v>
+        <v>q12</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
       </c>
       <c r="D13" t="str">
-        <v>控制倾向</v>
+        <v>教育一致性</v>
       </c>
       <c r="E13" t="str">
-        <v>家长会具体指定学校应该如何处理。</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>AGREE_5</v>
+        <v>这位家长尊重我的专业判断与教学决策</v>
       </c>
       <c r="G13" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I13" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J13" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
+        <v>是</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="B14" t="str">
-        <v>p4</v>
+        <v>q13</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
       </c>
       <c r="D14" t="str">
-        <v>控制倾向</v>
+        <v>教育一致性</v>
       </c>
       <c r="E14" t="str">
-        <v>家长对学校既有安排提出较多质疑。</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>AGREE_5</v>
+        <v>即使存在分歧，这位家长也能配合执行学校的统一安排</v>
       </c>
       <c r="G14" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I14" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J14" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
+        <v>是</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="B15" t="str">
-        <v>p5</v>
+        <v>q14</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
       </c>
       <c r="D15" t="str">
-        <v>信任基础</v>
+        <v>教育一致性</v>
       </c>
       <c r="E15" t="str">
-        <v>家长相信教师是出于孩子利益在做判断。</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v>AGREE_5</v>
+        <v>这位家长在孩子面前维护学校与教师的权威，不唱反调</v>
       </c>
       <c r="G15" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I15" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J15" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>是</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="B16" t="str">
-        <v>p6</v>
+        <v>q15</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
       </c>
       <c r="D16" t="str">
-        <v>信任基础</v>
+        <v>教育一致性</v>
       </c>
       <c r="E16" t="str">
-        <v>过去的沟通中，家长兑现过共同约定。</v>
+        <v/>
       </c>
       <c r="F16" t="str">
-        <v>AGREE_5</v>
+        <v>这位家长在家庭教育中能与学校要求保持一致、形成合力</v>
       </c>
       <c r="G16" t="str">
-        <v>是</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>1</v>
+        <v>AGREE_5</v>
       </c>
       <c r="I16" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J16" t="str">
-        <v>compute</v>
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
+        <v>是</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B17" t="str">
+        <v>q16</v>
+      </c>
+      <c r="C17" t="str">
+        <v>single</v>
+      </c>
+      <c r="D17" t="str">
+        <v>信任关系</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>我信任这位家长在孩子教育上的判断力</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I17" t="str">
+        <v>否</v>
+      </c>
+      <c r="J17" t="str">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
+        <v>是</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B18" t="str">
+        <v>q17</v>
+      </c>
+      <c r="C18" t="str">
+        <v>single</v>
+      </c>
+      <c r="D18" t="str">
+        <v>信任关系</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>我相信这位家长会履行与学校达成的约定</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I18" t="str">
+        <v>否</v>
+      </c>
+      <c r="J18" t="str">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>是</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B19" t="str">
+        <v>q18</v>
+      </c>
+      <c r="C19" t="str">
+        <v>single</v>
+      </c>
+      <c r="D19" t="str">
+        <v>信任关系</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>我认为这位家长诚实可靠、言出必行</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I19" t="str">
+        <v>否</v>
+      </c>
+      <c r="J19" t="str">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
+        <v>是</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B20" t="str">
+        <v>q19</v>
+      </c>
+      <c r="C20" t="str">
+        <v>single</v>
+      </c>
+      <c r="D20" t="str">
+        <v>信任关系</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>即使有分歧，我仍相信这位家长的出发点是为孩子好</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I20" t="str">
+        <v>否</v>
+      </c>
+      <c r="J20" t="str">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
+        <v>是</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B21" t="str">
+        <v>q20</v>
+      </c>
+      <c r="C21" t="str">
+        <v>single</v>
+      </c>
+      <c r="D21" t="str">
+        <v>信任关系</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>我相信这位家长会优先把孩子利益放在首位</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I21" t="str">
+        <v>否</v>
+      </c>
+      <c r="J21" t="str">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
+        <v>是</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B22" t="str">
+        <v>q21</v>
+      </c>
+      <c r="C22" t="str">
+        <v>single</v>
+      </c>
+      <c r="D22" t="str">
+        <v>参与效能</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>当我提出建议时，这位家长会积极回应而非敷衍</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I22" t="str">
+        <v>否</v>
+      </c>
+      <c r="J22" t="str">
+        <v>1</v>
+      </c>
+      <c r="K22" t="str">
+        <v>是</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B23" t="str">
+        <v>q22</v>
+      </c>
+      <c r="C23" t="str">
+        <v>single</v>
+      </c>
+      <c r="D23" t="str">
+        <v>参与效能</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>这位家长能将我的反馈转化为实际的教育行动</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I23" t="str">
+        <v>否</v>
+      </c>
+      <c r="J23" t="str">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>是</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B24" t="str">
+        <v>q23</v>
+      </c>
+      <c r="C24" t="str">
+        <v>single</v>
+      </c>
+      <c r="D24" t="str">
+        <v>参与效能</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>孩子出现问题时，这位家长能及时配合解决</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I24" t="str">
+        <v>否</v>
+      </c>
+      <c r="J24" t="str">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>是</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B25" t="str">
+        <v>q24</v>
+      </c>
+      <c r="C25" t="str">
+        <v>single</v>
+      </c>
+      <c r="D25" t="str">
+        <v>参与效能</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>这位家长重视并采纳我给出的教育建议</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I25" t="str">
+        <v>否</v>
+      </c>
+      <c r="J25" t="str">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>是</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B26" t="str">
+        <v>q25</v>
+      </c>
+      <c r="C26" t="str">
+        <v>single</v>
+      </c>
+      <c r="D26" t="str">
+        <v>参与效能</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>这位家长在家庭教育中的配合能见到实际改善效果</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I26" t="str">
+        <v>否</v>
+      </c>
+      <c r="J26" t="str">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>是</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B27" t="str">
+        <v>q26</v>
+      </c>
+      <c r="C27" t="str">
+        <v>single</v>
+      </c>
+      <c r="D27" t="str">
+        <v>危机响应</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>当孩子出现突发状况时，这位家长能保持冷静、理性沟通</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I27" t="str">
+        <v>否</v>
+      </c>
+      <c r="J27" t="str">
+        <v>1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>是</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B28" t="str">
+        <v>q27</v>
+      </c>
+      <c r="C28" t="str">
+        <v>single</v>
+      </c>
+      <c r="D28" t="str">
+        <v>危机响应</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>这位家长在危机时刻愿意配合学校的处置安排</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I28" t="str">
+        <v>否</v>
+      </c>
+      <c r="J28" t="str">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>是</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B29" t="str">
+        <v>q28</v>
+      </c>
+      <c r="C29" t="str">
+        <v>single</v>
+      </c>
+      <c r="D29" t="str">
+        <v>危机响应</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>这位家长不会在危机中情绪化地指责或推诿责任</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I29" t="str">
+        <v>否</v>
+      </c>
+      <c r="J29" t="str">
+        <v>1</v>
+      </c>
+      <c r="K29" t="str">
+        <v>是</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B30" t="str">
+        <v>q29</v>
+      </c>
+      <c r="C30" t="str">
+        <v>single</v>
+      </c>
+      <c r="D30" t="str">
+        <v>危机响应</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>这位家长能在危机后与我共同复盘、落实预防措施</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I30" t="str">
+        <v>否</v>
+      </c>
+      <c r="J30" t="str">
+        <v>1</v>
+      </c>
+      <c r="K30" t="str">
+        <v>是</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>HS_S1</v>
+      </c>
+      <c r="B31" t="str">
+        <v>q30</v>
+      </c>
+      <c r="C31" t="str">
+        <v>single</v>
+      </c>
+      <c r="D31" t="str">
+        <v>危机响应</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>这位家长信任学校在危机处理中的专业性，不激化矛盾</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I31" t="str">
+        <v>否</v>
+      </c>
+      <c r="J31" t="str">
+        <v>1</v>
+      </c>
+      <c r="K31" t="str">
+        <v>是</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>HS_S2</v>
+      </c>
+      <c r="B32" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C32" t="str">
+        <v>single</v>
+      </c>
+      <c r="D32" t="str">
+        <v>红线风险</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>近期出现法律途径对抗（起诉、向主管部门举报等）</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I32" t="str">
+        <v>否</v>
+      </c>
+      <c r="J32" t="str">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>是</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>HS_S2</v>
+      </c>
+      <c r="B33" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C33" t="str">
+        <v>single</v>
+      </c>
+      <c r="D33" t="str">
+        <v>红线风险</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>学生出现自伤倾向或相关风险信号</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I33" t="str">
+        <v>否</v>
+      </c>
+      <c r="J33" t="str">
+        <v>1</v>
+      </c>
+      <c r="K33" t="str">
+        <v>是</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>HS_S2</v>
+      </c>
+      <c r="B34" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C34" t="str">
+        <v>single</v>
+      </c>
+      <c r="D34" t="str">
+        <v>红线风险</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>家长在公开媒体（网络平台、媒体等）发布攻击性内容</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I34" t="str">
+        <v>否</v>
+      </c>
+      <c r="J34" t="str">
+        <v>1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>是</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>HS_S2</v>
+      </c>
+      <c r="B35" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C35" t="str">
+        <v>single</v>
+      </c>
+      <c r="D35" t="str">
+        <v>红线风险</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>家校夹击导致学生出现严重适应障碍</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I35" t="str">
+        <v>否</v>
+      </c>
+      <c r="J35" t="str">
+        <v>1</v>
+      </c>
+      <c r="K35" t="str">
+        <v>是</v>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>HS_S2</v>
+      </c>
+      <c r="B36" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C36" t="str">
+        <v>single</v>
+      </c>
+      <c r="D36" t="str">
+        <v>红线风险</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>家长对教师或学校人员发出人身安全威胁</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I36" t="str">
+        <v>否</v>
+      </c>
+      <c r="J36" t="str">
+        <v>1</v>
+      </c>
+      <c r="K36" t="str">
+        <v>是</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>HS_S2</v>
+      </c>
+      <c r="B37" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C37" t="str">
+        <v>single</v>
+      </c>
+      <c r="D37" t="str">
+        <v>红线风险</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>家校沟通已完全断绝（沟通渠道全部失效）</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I37" t="str">
+        <v>否</v>
+      </c>
+      <c r="J37" t="str">
+        <v>1</v>
+      </c>
+      <c r="K37" t="str">
+        <v>是</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>HS_S2</v>
+      </c>
+      <c r="B38" t="str">
+        <v>q7</v>
+      </c>
+      <c r="C38" t="str">
+        <v>single</v>
+      </c>
+      <c r="D38" t="str">
+        <v>红线风险</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>家长提出强制转学或退学要求</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I38" t="str">
+        <v>否</v>
+      </c>
+      <c r="J38" t="str">
+        <v>1</v>
+      </c>
+      <c r="K38" t="str">
+        <v>是</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>HS_S2</v>
+      </c>
+      <c r="B39" t="str">
+        <v>q8</v>
+      </c>
+      <c r="C39" t="str">
+        <v>single</v>
+      </c>
+      <c r="D39" t="str">
+        <v>红线风险</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>多名家长联合对学校施压</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I39" t="str">
+        <v>否</v>
+      </c>
+      <c r="J39" t="str">
+        <v>1</v>
+      </c>
+      <c r="K39" t="str">
+        <v>是</v>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1156,13 +2738,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>几乎没有</v>
+        <v>完全不符合</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1170,13 +2752,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>很少</v>
+        <v>比较不符合</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1184,13 +2766,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>有时</v>
+        <v>一般</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1198,13 +2780,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>经常</v>
+        <v>比较符合</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1212,13 +2794,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>几乎每天</v>
+        <v>非常符合</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
@@ -1226,84 +2808,42 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AGREE_5</v>
+        <v>YES_NO</v>
       </c>
       <c r="B7" t="str">
         <v>1</v>
       </c>
       <c r="C7" t="str">
-        <v>完全不符合</v>
+        <v>否</v>
       </c>
       <c r="D7" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AGREE_5</v>
+        <v>YES_NO</v>
       </c>
       <c r="B8" t="str">
         <v>2</v>
       </c>
       <c r="C8" t="str">
-        <v>比较不符合</v>
+        <v>是</v>
       </c>
       <c r="D8" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B9" t="str">
-        <v>3</v>
-      </c>
-      <c r="C9" t="str">
-        <v>一般</v>
-      </c>
-      <c r="D9" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B10" t="str">
-        <v>4</v>
-      </c>
-      <c r="C10" t="str">
-        <v>比较符合</v>
-      </c>
-      <c r="D10" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B11" t="str">
-        <v>5</v>
-      </c>
-      <c r="C11" t="str">
-        <v>非常符合</v>
-      </c>
-      <c r="D11" t="str">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1333,19 +2873,25 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
+      <c r="J1" t="str">
+        <v>常模均值</v>
+      </c>
+      <c r="K1" t="str">
+        <v>常模标准差</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>HS_COOP</v>
+        <v>HS_S1D1</v>
       </c>
       <c r="C2" t="str">
-        <v>配合度</v>
+        <v>沟通质量</v>
       </c>
       <c r="D2" t="str">
-        <v>coop1,coop2,coop3</v>
+        <v>q1,q2,q3,q4,q5</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1354,27 +2900,33 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>配合度维度</v>
+        <v>双向性/及时性：信息能否顺畅及时触达并得到确认</v>
       </c>
       <c r="H2" t="str">
-        <v>家长回应慢、不参与共同行动</v>
+        <v>建立稳定固定的沟通渠道与联系节奏，重要信息送达有确认流程</v>
       </c>
       <c r="I2" t="str">
-        <v>配合度良好</v>
+        <v>信息传递滞后或失真，家长被动等待通知，沟通氛围紧张、问题被掩盖</v>
+      </c>
+      <c r="J2" t="str">
+        <v>4</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>HS_ATTITUDE</v>
+        <v>HS_S1D2</v>
       </c>
       <c r="C3" t="str">
-        <v>沟通态度</v>
+        <v>角色边界</v>
       </c>
       <c r="D3" t="str">
-        <v>att1,att2,att3</v>
+        <v>q6,q7,q8,q9,q10</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1383,27 +2935,33 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>沟通态度维度</v>
+        <v>职责清晰度：家长是否越界打扰、过度介入、不守公共渠道规则</v>
       </c>
       <c r="H3" t="str">
-        <v>出现不尊重、混淆事实与情绪甚至威胁行为</v>
+        <v>沟通时段与响应预期明确，家校职责分工清晰，家长尊重教师专业空间</v>
       </c>
       <c r="I3" t="str">
-        <v>沟通态度可控</v>
+        <v>非工作时间频繁打扰，过度介入班级事务或替教师做决策，公开渠道发布越界言论</v>
+      </c>
+      <c r="J3" t="str">
+        <v>4</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>HS_QUICK</v>
+        <v>HS_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>HS_CONTAINER</v>
+        <v>HS_S1D3</v>
       </c>
       <c r="C4" t="str">
-        <v>关系容器</v>
+        <v>教育一致性</v>
       </c>
       <c r="D4" t="str">
-        <v>con1,con2,con3</v>
+        <v>q11,q12,q13,q14,q15</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1412,27 +2970,33 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>关系容器维度</v>
+        <v>价值观/规则协调：家校理念与规则是否一致、能否形成合力</v>
       </c>
       <c r="H4" t="str">
-        <v>关系无法承受坦诚讨论</v>
+        <v>教育理念与规则充分对齐，分歧先私下达成共识，家庭配合有可操作指引</v>
       </c>
       <c r="I4" t="str">
-        <v>关系容器充足</v>
+        <v>家校要求互相矛盾，家长在孩子面前否定教师，理念冲突导致学校安排无法落地</v>
+      </c>
+      <c r="J4" t="str">
+        <v>4</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>HS_ANXIETY</v>
+        <v>HS_S1D4</v>
       </c>
       <c r="C5" t="str">
-        <v>焦虑水平</v>
+        <v>信任关系</v>
       </c>
       <c r="D5" t="str">
-        <v>p1,p2</v>
+        <v>q16,q17,q18,q19,q20</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1441,27 +3005,33 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>焦虑水平维度</v>
+        <v>尊重/心理安全感：家长是否相信教师出于孩子利益做判断并履约</v>
       </c>
       <c r="H5" t="str">
-        <v>家长处于高焦虑，难以接收复杂信息</v>
+        <v>以小事守信积累信任，重大事项透明告知，冲突时先确认善意动机</v>
       </c>
       <c r="I5" t="str">
-        <v>情绪相对平稳</v>
+        <v>互相猜疑、任何举措都被解读为不怀好意，约定形同虚设，危机时对立激化</v>
+      </c>
+      <c r="J5" t="str">
+        <v>4</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>HS_CONTROL</v>
+        <v>HS_S1D5</v>
       </c>
       <c r="C6" t="str">
-        <v>控制倾向</v>
+        <v>参与效能</v>
       </c>
       <c r="D6" t="str">
-        <v>p3,p4</v>
+        <v>q21,q22,q23,q24,q25</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1470,27 +3040,33 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>控制倾向维度</v>
+        <v>实际效果与感知：家长配合能否转化为实际教育行动并见到效果</v>
       </c>
       <c r="H6" t="str">
-        <v>家长倾向于主导教育方式并质疑学校安排</v>
+        <v>建议具体可执行有期限并约定反馈节点，对微小进步及时肯定，形成跟踪闭环</v>
       </c>
       <c r="I6" t="str">
-        <v>愿意接受学校专业判断</v>
+        <v>口头答应但无行动，问题反复出现，配合缺乏持续性与闭环，教师单方面费力</v>
+      </c>
+      <c r="J6" t="str">
+        <v>4</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>HS_PARENT_TYPE</v>
+        <v>HS_S1</v>
       </c>
       <c r="B7" t="str">
-        <v>HS_TRUST</v>
+        <v>HS_S1D6</v>
       </c>
       <c r="C7" t="str">
-        <v>信任基础</v>
+        <v>危机响应</v>
       </c>
       <c r="D7" t="str">
-        <v>p5,p6</v>
+        <v>q26,q27,q28,q29,q30</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1499,18 +3075,59 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>信任基础维度</v>
+        <v>突发事件协同：危机时刻能否冷静理性配合处置、事后共同复盘</v>
       </c>
       <c r="H7" t="str">
-        <v>对学校缺乏基本信任</v>
+        <v>提前约定危机联络人与应急流程，危机中先共情给确定性再谈事实，事后共同复盘</v>
       </c>
       <c r="I7" t="str">
-        <v>有较好的信任基础</v>
+        <v>危机时情绪失控指责教师，拒绝配合处置或撒手不管，危机后无复盘、问题周期性重演</v>
+      </c>
+      <c r="J7" t="str">
+        <v>4</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HS_S2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>HS_S2D1</v>
+      </c>
+      <c r="C8" t="str">
+        <v>红线风险</v>
+      </c>
+      <c r="D8" t="str">
+        <v>q1,q2,q3,q4,q5,q6,q7,q8</v>
+      </c>
+      <c r="E8" t="str">
+        <v>sum</v>
+      </c>
+      <c r="F8" t="str">
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
+        <v>R1-R8 红线命中项数，任一命中即触发五级危机干预</v>
+      </c>
+      <c r="H8" t="str">
+        <v>命中红线项数越多，危机程度越高</v>
+      </c>
+      <c r="I8" t="str">
+        <v>未命中任何红线</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K8"/>
   </ignoredErrors>
 </worksheet>
 </file>